--- a/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64984_completo.xlsx
+++ b/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64984_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9d44c9a0ee3c4f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Red54c3611d2d40fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,126 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    229.7673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    167.9170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    180.8585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    206.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    245.2912</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    166.8291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    172.0364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    169.5593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64984_completo.xlsx
+++ b/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64984_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Red54c3611d2d40fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R59b41e5fabba4763"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.4301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    159.1340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    131.1227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    144.8048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.1742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    140.7586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.6450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    145.6616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    145.9643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    154.8726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    178.2322</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    167.9028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    167.9210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    234.9566</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    135.9223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    146.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    146.5640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    156.6042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    174.8377</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    178.0023</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    238.5182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    271.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    287.2360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    284.4848</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    243.0949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    173.3727</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    166.2786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    160.5385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    203.3793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    190.4897</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    185.5644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    215.0186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    160.3871</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.4072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    136.0924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    147.4125</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    151.7065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    157.4964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    146.2532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    145.7386</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.1154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    144.8072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    143.4430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    146.1238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    157.6760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    169.5328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    203.9324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
